--- a/武器模块.xlsx
+++ b/武器模块.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icfer\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icfer\Pictures\zmd筛选基质\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF1910C-73D4-43D4-AEB7-AF0C59DA81CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2007F696-908B-4613-BC44-B1097B57D35A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="147">
   <si>
     <t>武器</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -436,12 +436,207 @@
     <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/使命必达.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>O.B.J.术识</t>
+  </si>
+  <si>
+    <t>布道自由</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗效率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>迷失荒野</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莫奈何</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昂扬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悼亡诗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理性告别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O.B.J.迅极</t>
+  </si>
+  <si>
+    <t>作品：众生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>向心之引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O.B.J.尖峰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嵌合正义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O.B.J.重荷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>终点之声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>古渠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>探骊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>仰止</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O.B.J.轻芒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>十二问</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>逐鳞3.0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坚城铸造者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢铁余音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巧技</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/O.B.J.术识.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/布道自由.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/迷失荒野.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/莫奈何.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/悼亡诗.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/理性告别.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/O.B.J.迅极.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/作品：众生.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/向心之引.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/O.B.J.尖峰.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/嵌合正义.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/O.B.J.重荷.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/终点之声.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/古渠.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/探骊.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/仰止.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/O.B.J.轻芒.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/十二问.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/逐鳞3.0.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/坚城铸造者.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/icfer233/picture-bed1/main/zmd/钢铁余音.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⭐</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +687,17 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -514,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -526,6 +732,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -807,39 +1030,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H59"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.75" customWidth="1"/>
-    <col min="2" max="2" width="26.875" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="26.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9" style="5"/>
+    <col min="4" max="5" width="9" style="3"/>
+    <col min="6" max="6" width="13.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>99</v>
       </c>
@@ -862,7 +1087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>98</v>
       </c>
@@ -885,7 +1110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>97</v>
       </c>
@@ -908,7 +1133,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>96</v>
       </c>
@@ -931,7 +1156,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>95</v>
       </c>
@@ -954,7 +1179,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>94</v>
       </c>
@@ -977,7 +1202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>93</v>
       </c>
@@ -1000,7 +1225,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>92</v>
       </c>
@@ -1023,7 +1248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>91</v>
       </c>
@@ -1046,7 +1271,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>90</v>
       </c>
@@ -1069,7 +1294,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>89</v>
       </c>
@@ -1092,7 +1317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>88</v>
       </c>
@@ -1115,7 +1340,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>87</v>
       </c>
@@ -1138,7 +1363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>86</v>
       </c>
@@ -1161,7 +1386,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>85</v>
       </c>
@@ -1184,7 +1409,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>84</v>
       </c>
@@ -1207,7 +1432,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>83</v>
       </c>
@@ -1230,7 +1455,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>82</v>
       </c>
@@ -1253,7 +1478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>81</v>
       </c>
@@ -1276,7 +1501,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>80</v>
       </c>
@@ -1299,7 +1524,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>79</v>
       </c>
@@ -1322,7 +1547,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>78</v>
       </c>
@@ -1345,7 +1570,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>77</v>
       </c>
@@ -1368,7 +1593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>76</v>
       </c>
@@ -1391,7 +1616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>75</v>
       </c>
@@ -1414,7 +1639,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>74</v>
       </c>
@@ -1437,7 +1662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>73</v>
       </c>
@@ -1460,7 +1685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>72</v>
       </c>
@@ -1483,7 +1708,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>71</v>
       </c>
@@ -1506,7 +1731,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>7</v>
       </c>
@@ -1528,6 +1753,575 @@
       <c r="G31" s="3" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" s="6"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="6"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="6"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" s="6"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="6"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="6"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="6"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="7"/>
+      <c r="H53" s="6"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="6"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="6"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="6"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="7"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="6"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
+      <c r="H56" s="6"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="6"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="6"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="6"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="7"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="6"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1562,6 +2356,27 @@
     <hyperlink ref="A4" r:id="rId28" xr:uid="{A7C2A37A-C94B-4560-80E1-40E759177E6C}"/>
     <hyperlink ref="A3" r:id="rId29" xr:uid="{0B0E22BF-E448-4E38-B1C0-B7FA1DE85C06}"/>
     <hyperlink ref="A2" r:id="rId30" xr:uid="{C4D0028F-2D94-457A-B69C-35ECC546CE4D}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{64C401CD-B1F7-471E-98BE-71FF21F7C710}"/>
+    <hyperlink ref="A33" r:id="rId32" xr:uid="{63974529-0760-48A4-885C-8534128A185C}"/>
+    <hyperlink ref="A34" r:id="rId33" xr:uid="{633826C9-1C75-40A1-83F1-A3324DD7882D}"/>
+    <hyperlink ref="A35" r:id="rId34" xr:uid="{3ABBF405-8747-4C8B-A677-B61E877191A3}"/>
+    <hyperlink ref="A36" r:id="rId35" xr:uid="{FC8A67E7-BE98-4E0C-80C5-487D218C61D1}"/>
+    <hyperlink ref="A37" r:id="rId36" xr:uid="{B061A1E8-38F7-45AF-B875-92305F073ED8}"/>
+    <hyperlink ref="A38" r:id="rId37" xr:uid="{F9FB2D1F-AAC9-4A0F-930B-2117A8591853}"/>
+    <hyperlink ref="A39" r:id="rId38" xr:uid="{92C7EE87-203F-4A26-902C-1CB97F68D082}"/>
+    <hyperlink ref="A40" r:id="rId39" xr:uid="{277BD23D-3A78-4AB8-A5AF-6BED99ADFA33}"/>
+    <hyperlink ref="A41" r:id="rId40" xr:uid="{291C6918-11F2-4F16-886C-1AC303116FE2}"/>
+    <hyperlink ref="A42" r:id="rId41" xr:uid="{6B30F8EA-DFF9-4883-8723-D99C083843D7}"/>
+    <hyperlink ref="A43" r:id="rId42" xr:uid="{AE6683E6-CC05-482A-87C9-732468BF34E8}"/>
+    <hyperlink ref="A44" r:id="rId43" xr:uid="{3F5415C9-B826-428F-8477-C69D02CA9B75}"/>
+    <hyperlink ref="A45" r:id="rId44" xr:uid="{4124B4B2-65A7-482B-AC0D-93CF96FD9AC3}"/>
+    <hyperlink ref="A46" r:id="rId45" xr:uid="{2D91E6B5-E11C-4B9C-9078-6CC098913533}"/>
+    <hyperlink ref="A47" r:id="rId46" xr:uid="{0E5A7575-8B79-4CBA-90B5-ED6742E7697D}"/>
+    <hyperlink ref="A48" r:id="rId47" xr:uid="{2D922DF4-04C6-4F78-AC0F-779E1B8F42B5}"/>
+    <hyperlink ref="A49" r:id="rId48" xr:uid="{70F00D1E-91C4-40E4-AEC7-9D3563E49189}"/>
+    <hyperlink ref="A50" r:id="rId49" xr:uid="{3489AD77-5CBB-433A-BE03-95A75B463501}"/>
+    <hyperlink ref="A51" r:id="rId50" xr:uid="{D94644E8-35CD-4D8C-A1F6-E2640A8E7B4D}"/>
+    <hyperlink ref="A52" r:id="rId51" xr:uid="{5C155B4F-70E6-4A59-AC7E-0331FAFCBB7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
